--- a/jogos_2025-10-12.xlsx
+++ b/jogos_2025-10-12.xlsx
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1052,17 +1052,17 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>UD Granadilla Tenerife</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>UD Granadilla Tenerife</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Osasuna II</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2600,17 +2600,17 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Real Madrid II</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Pontevedra CF</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Real Madrid II</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Pontevedra CF</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Osasuna II</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3987,22 +3987,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Qingdao Red Lions</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Guangxi Baoyun</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Qingdao Red Lions</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Guangxi Baoyun</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7083,22 +7083,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7158,10 +7158,10 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AA52" t="n">
         <v>0</v>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>CE Sabadell FC</t>
+          <t>Barakaldo CF</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>CD Teruel</t>
+          <t>Athletic Club II</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>Sevilla II</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>FC Cartagena</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Celta de Vigo II</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Ourense CF</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Racing Santander II</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Hércules CF</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Atlético Madrid II</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Arenas de Getxo</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>CD Lugo</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Hércules CF</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Atlético Madrid II</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Sevilla II</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>FC Cartagena</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Juventud Torremolinos</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>UD Ibiza</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>CE Sabadell FC</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>CD Teruel</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Juventud Torremolinos</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>UD Ibiza</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9405,22 +9405,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9480,10 +9480,10 @@
         <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z70" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Arenas de Getxo</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>CD Lugo</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Racing Santander II</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9921,7 +9921,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10179,7 +10179,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Unionistas de Salamanca CF</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mérida AD</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Barakaldo CF</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Athletic Club II</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Celta de Vigo II</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ourense CF</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Unionistas de Salamanca CF</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Mérida AD</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11985,7 +11985,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13275,7 +13275,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13533,7 +13533,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13920,7 +13920,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14446,12 +14446,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14704,12 +14704,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14833,12 +14833,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -15091,12 +15091,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15117,13 +15117,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M114" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N114" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15156,10 +15156,10 @@
         <v>0</v>
       </c>
       <c r="Y114" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Z114" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA114" t="n">
         <v>0</v>
@@ -15220,12 +15220,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15246,13 +15246,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M115" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -15285,10 +15285,10 @@
         <v>0</v>
       </c>
       <c r="Y115" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Z115" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA115" t="n">
         <v>0</v>

--- a/jogos_2025-10-12.xlsx
+++ b/jogos_2025-10-12.xlsx
@@ -1020,7 +1020,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1052,17 +1052,17 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>SS Reyes</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>Rayo Vallecano II</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>UD Granadilla Tenerife</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>UD Granadilla Tenerife</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Osasuna II</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SS Reyes</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rayo Vallecano II</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2600,17 +2600,17 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.58</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Real Madrid II</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Pontevedra CF</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Real Madrid II</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Pontevedra CF</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Osasuna II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3987,22 +3987,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4503,22 +4503,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Qingdao Red Lions</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Guangxi Baoyun</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Qingdao Red Lions</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Guangxi Baoyun</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5158,12 +5158,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5416,12 +5416,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Potenza Calcio</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Latina</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Potenza Calcio</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Latina</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5793,7 +5793,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -7083,22 +7083,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7158,10 +7158,10 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z52" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AA52" t="n">
         <v>0</v>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Barakaldo CF</t>
+          <t>CE Sabadell FC</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Athletic Club II</t>
+          <t>CD Teruel</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Sevilla II</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>FC Cartagena</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Celta de Vigo II</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ourense CF</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Racing Santander II</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Hércules CF</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Atlético Madrid II</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Arenas de Getxo</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>CD Lugo</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8254,12 +8254,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Hércules CF</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Atlético Madrid II</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Sevilla II</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>FC Cartagena</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Eibar II</t>
+          <t>Juventud Torremolinos</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>SD Ejea</t>
+          <t>UD Ibiza</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Eibar II</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>SD Ejea</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9147,7 +9147,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -9157,12 +9157,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>CE Sabadell FC</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>CD Teruel</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -9286,12 +9286,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Juventud Torremolinos</t>
+          <t>Coruxo</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>UD Ibiza</t>
+          <t>Bergantiños</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9405,22 +9405,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9480,10 +9480,10 @@
         <v>0</v>
       </c>
       <c r="Y70" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z70" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AA70" t="n">
         <v>0</v>
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>Arenas de Getxo</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>CD Lugo</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9663,7 +9663,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Racing Santander II</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9921,7 +9921,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Coruxo</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Bergantiños</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10179,7 +10179,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Unionistas de Salamanca CF</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>Mérida AD</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10437,7 +10437,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Barakaldo CF</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>Athletic Club II</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Celta de Vigo II</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Ourense CF</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Unionistas de Salamanca CF</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mérida AD</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11985,7 +11985,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>UE Sant Andreu</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Valencia II</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>UE Sant Andreu</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Valencia II</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -13275,7 +13275,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13533,7 +13533,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Atlético Ottawa</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Operário PR</t>
+          <t>Vancouver FC</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13920,7 +13920,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Atlético Ottawa</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vancouver FC</t>
+          <t>Operário PR</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Mount Pleasant Academy FC</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Chapelton</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Racing United</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Spanish Town Police FC</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Mount Pleasant Academy FC</t>
+          <t>Cavalier</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Chapelton</t>
+          <t>Portmore United</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14446,12 +14446,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14704,12 +14704,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Cavalier</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Portmore United</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14833,12 +14833,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Racing United</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Spanish Town Police FC</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -15091,12 +15091,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>América Mineiro</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15117,13 +15117,13 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="M114" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O114" t="n">
         <v>0</v>
@@ -15156,10 +15156,10 @@
         <v>0</v>
       </c>
       <c r="Y114" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Z114" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AA114" t="n">
         <v>0</v>
@@ -15220,12 +15220,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>América Mineiro</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15246,13 +15246,13 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="M115" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N115" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O115" t="n">
         <v>0</v>
@@ -15285,10 +15285,10 @@
         <v>0</v>
       </c>
       <c r="Y115" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Z115" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AA115" t="n">
         <v>0</v>

--- a/jogos_2025-10-12.xlsx
+++ b/jogos_2025-10-12.xlsx
@@ -678,13 +678,13 @@
         <v>1.87</v>
       </c>
       <c r="O2" t="n">
-        <v>3.71</v>
+        <v>3.35</v>
       </c>
       <c r="P2" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.52</v>
+        <v>2.77</v>
       </c>
       <c r="R2" t="n">
         <v>1.34</v>
@@ -693,7 +693,7 @@
         <v>3.2</v>
       </c>
       <c r="T2" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="U2" t="n">
         <v>1.5</v>
@@ -702,28 +702,28 @@
         <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X2" t="n">
         <v>4</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="AC2" t="n">
         <v>1.62</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.19</v>
+        <v>2.12</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
@@ -736,10 +736,10 @@
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.22</v>
+        <v>1.55</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>UD Granadilla Tenerife</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>UB Conquense</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1314,61 +1314,61 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>1.48</v>
+        <v>2.7</v>
       </c>
       <c r="M7" t="n">
-        <v>4.15</v>
+        <v>3.4</v>
       </c>
       <c r="N7" t="n">
-        <v>6</v>
+        <v>2.4</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.44</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.75</v>
+        <v>1.97</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.95</v>
+        <v>1.73</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
@@ -1381,10 +1381,10 @@
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Juventud Torremolinos</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>UD Ibiza</t>
+          <t>Las Palmas II</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1443,61 +1443,61 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3</v>
+        <v>1.95</v>
       </c>
       <c r="M8" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N8" t="n">
-        <v>2.3</v>
+        <v>4.1</v>
       </c>
       <c r="O8" t="n">
-        <v>4.49</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
         <v>2.4</v>
       </c>
-      <c r="Y8" t="n">
-        <v>2.2</v>
-      </c>
       <c r="Z8" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>Real Valladolid II</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>CD Lealtad</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1568,17 +1568,17 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.66</v>
+        <v>2.05</v>
       </c>
       <c r="M9" t="n">
-        <v>2.82</v>
+        <v>3.3</v>
       </c>
       <c r="N9" t="n">
-        <v>2.58</v>
+        <v>3.45</v>
       </c>
       <c r="O9" t="n">
         <v>0</v>
@@ -1611,10 +1611,10 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Atletico Madrid W</t>
+          <t>Juventud Torremolinos</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Barcelona W</t>
+          <t>UD Ibiza</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1701,61 +1701,61 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="M10" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O10" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="X10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA10" t="n">
         <v>5</v>
       </c>
-      <c r="N10" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>0</v>
-      </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1768,10 +1768,10 @@
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RSD Alcalá</t>
+          <t>Deportiva Minera</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Quintanar del Rey</t>
+          <t>Recreativo de Huelva</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1830,61 +1830,61 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.05</v>
+        <v>2.55</v>
       </c>
       <c r="M11" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="N11" t="n">
-        <v>3.9</v>
+        <v>2.55</v>
       </c>
       <c r="O11" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.55</v>
+        <v>2</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.45</v>
+        <v>1.72</v>
       </c>
       <c r="AA11" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
@@ -1897,10 +1897,10 @@
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Andratx</t>
+          <t>UD Granadilla Tenerife</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CD Atlético Baleares</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.65</v>
+        <v>1.48</v>
       </c>
       <c r="M12" t="n">
-        <v>3.15</v>
+        <v>4.15</v>
       </c>
       <c r="N12" t="n">
-        <v>2.05</v>
+        <v>6</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1992,16 +1992,16 @@
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.5</v>
+        <v>1.75</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.5</v>
+        <v>1.95</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>CF Fuenlabrada</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Intercity</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2088,61 +2088,61 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.79</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Atletico Madrid W</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lusitânia</t>
+          <t>Barcelona W</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2217,13 +2217,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2256,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Real Valladolid II</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>CD Lealtad</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2342,17 +2342,17 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.05</v>
+        <v>2.66</v>
       </c>
       <c r="M15" t="n">
-        <v>3.3</v>
+        <v>2.82</v>
       </c>
       <c r="N15" t="n">
-        <v>3.45</v>
+        <v>2.58</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2385,10 +2385,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Castellón II</t>
+          <t>Tenerife II</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ibiza Islas Pitiusas</t>
+          <t>UD Socuéllamos</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2475,61 +2475,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.35</v>
+        <v>1.37</v>
       </c>
       <c r="M16" t="n">
-        <v>3.3</v>
+        <v>3.95</v>
       </c>
       <c r="N16" t="n">
-        <v>2.9</v>
+        <v>10</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>5.85</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.77</v>
+        <v>2.25</v>
       </c>
       <c r="Z16" t="n">
-        <v>1.93</v>
+        <v>1.57</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
@@ -2542,10 +2542,10 @@
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AI16" t="n">
         <v>0</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Tenerife II</t>
+          <t>Machico</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>UD Socuéllamos</t>
+          <t>Os Limianos</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2604,61 +2604,61 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.37</v>
+        <v>2.66</v>
       </c>
       <c r="M17" t="n">
-        <v>3.95</v>
+        <v>2.82</v>
       </c>
       <c r="N17" t="n">
-        <v>10</v>
+        <v>2.58</v>
       </c>
       <c r="O17" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>5.85</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>3.98</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="AG17" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
         <v>0</v>
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Girona II</t>
+          <t>Real Jaén CF</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Porreres</t>
+          <t>UD Melilla</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2733,13 +2733,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.03</v>
+        <v>1.98</v>
       </c>
       <c r="M18" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="N18" t="n">
-        <v>3.65</v>
+        <v>3.95</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2772,10 +2772,10 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Real Jaén CF</t>
+          <t>Andratx</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>UD Melilla</t>
+          <t>CD Atlético Baleares</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2862,13 +2862,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.98</v>
+        <v>3.65</v>
       </c>
       <c r="M19" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="N19" t="n">
-        <v>3.95</v>
+        <v>2.05</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2895,16 +2895,16 @@
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Levante W</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sevilla W</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2991,61 +2991,61 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
@@ -3058,10 +3058,10 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
         <v>0</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,12 +3094,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Malaga II</t>
+          <t>Castellón II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Union Estepona CF</t>
+          <t>Ibiza Islas Pitiusas</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3120,14 +3120,14 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.6</v>
+        <v>2.35</v>
       </c>
       <c r="M21" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N21" t="n">
         <v>2.9</v>
       </c>
-      <c r="N21" t="n">
-        <v>2.85</v>
-      </c>
       <c r="O21" t="n">
         <v>0</v>
       </c>
@@ -3153,16 +3153,16 @@
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Deportiva Minera</t>
+          <t>Malaga II</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Recreativo de Huelva</t>
+          <t>Union Estepona CF</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3249,13 +3249,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="M22" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
       <c r="N22" t="n">
-        <v>2.55</v>
+        <v>2.85</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3282,16 +3282,16 @@
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>UCAM Murcia CF</t>
+          <t>Girona II</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Xerez Deportivo</t>
+          <t>Porreres</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.62</v>
+        <v>2.03</v>
       </c>
       <c r="M23" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="N23" t="n">
-        <v>5.6</v>
+        <v>3.65</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Machico</t>
+          <t>UCAM Murcia CF</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Os Limianos</t>
+          <t>Xerez Deportivo</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.66</v>
+        <v>1.62</v>
       </c>
       <c r="M24" t="n">
-        <v>2.82</v>
+        <v>3.5</v>
       </c>
       <c r="N24" t="n">
-        <v>2.58</v>
+        <v>5.6</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3729,7 +3729,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>CF Fuenlabrada</t>
+          <t>Levante W</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Intercity</t>
+          <t>Sevilla W</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3765,61 +3765,61 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="M26" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="N26" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="O26" t="n">
-        <v>3.79</v>
+        <v>3.44</v>
       </c>
       <c r="P26" t="n">
         <v>1.93</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.1</v>
+        <v>3.24</v>
       </c>
       <c r="R26" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="S26" t="n">
-        <v>2.47</v>
+        <v>2.41</v>
       </c>
       <c r="T26" t="n">
-        <v>3.12</v>
+        <v>3.28</v>
       </c>
       <c r="U26" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="V26" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="W26" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="X26" t="n">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.75</v>
+        <v>1.55</v>
       </c>
       <c r="AA26" t="n">
-        <v>3.88</v>
+        <v>4.25</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
@@ -3832,10 +3832,10 @@
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AI26" t="n">
         <v>0</v>
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Las Palmas II</t>
+          <t>Lusitânia</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,10 +3933,10 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3997,12 +3997,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>RSD Alcalá</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>UB Conquense</t>
+          <t>Quintanar del Rey</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4023,61 +4023,61 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.7</v>
+        <v>2.05</v>
       </c>
       <c r="M28" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="N28" t="n">
-        <v>2.4</v>
+        <v>3.9</v>
       </c>
       <c r="O28" t="n">
-        <v>3.44</v>
+        <v>3.06</v>
       </c>
       <c r="P28" t="n">
-        <v>1.98</v>
+        <v>1.83</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.12</v>
+        <v>4.15</v>
       </c>
       <c r="R28" t="n">
-        <v>1.44</v>
+        <v>1.58</v>
       </c>
       <c r="S28" t="n">
-        <v>2.59</v>
+        <v>2.26</v>
       </c>
       <c r="T28" t="n">
-        <v>3.09</v>
+        <v>3.72</v>
       </c>
       <c r="U28" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="V28" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W28" t="n">
-        <v>1.36</v>
+        <v>1.55</v>
       </c>
       <c r="X28" t="n">
-        <v>2.93</v>
+        <v>2.34</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.97</v>
+        <v>2.55</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.73</v>
+        <v>1.45</v>
       </c>
       <c r="AA28" t="n">
-        <v>3.58</v>
+        <v>5.25</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.21</v>
+        <v>1.09</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.82</v>
+        <v>2.17</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.87</v>
+        <v>1.58</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
@@ -4090,10 +4090,10 @@
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.4</v>
+        <v>1.54</v>
       </c>
       <c r="AI28" t="n">
         <v>0</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,12 +4255,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Monopoli</t>
+          <t>Burgos Promesas</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Salernitana</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,61 +4281,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.95</v>
+        <v>2.08</v>
       </c>
       <c r="M30" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="N30" t="n">
-        <v>2.3</v>
+        <v>3.35</v>
       </c>
       <c r="O30" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AA30" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
@@ -4348,10 +4348,10 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
         <v>0</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Burgos Promesas</t>
+          <t>Vis Pesaro</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4410,13 +4410,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.08</v>
+        <v>2.25</v>
       </c>
       <c r="M31" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="N31" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4449,10 +4449,10 @@
         <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Z31" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Vis Pesaro</t>
+          <t>Monopoli</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Salernitana</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4539,61 +4539,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.25</v>
+        <v>2.95</v>
       </c>
       <c r="M32" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N32" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O32" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="P32" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="T32" t="n">
         <v>3.1</v>
       </c>
-      <c r="N32" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" t="n">
-        <v>0</v>
-      </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
@@ -4606,10 +4606,10 @@
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI32" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Växjö</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4668,61 +4668,61 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.97</v>
+        <v>2.05</v>
       </c>
       <c r="M33" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
       <c r="N33" t="n">
-        <v>2.9</v>
+        <v>3.15</v>
       </c>
       <c r="O33" t="n">
-        <v>2.76</v>
+        <v>2.64</v>
       </c>
       <c r="P33" t="n">
-        <v>1.89</v>
+        <v>2.19</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.7</v>
+        <v>3.7</v>
       </c>
       <c r="R33" t="n">
-        <v>1.46</v>
+        <v>1.28</v>
       </c>
       <c r="S33" t="n">
-        <v>2.33</v>
+        <v>3.2</v>
       </c>
       <c r="T33" t="n">
-        <v>3.35</v>
+        <v>2.43</v>
       </c>
       <c r="U33" t="n">
-        <v>1.26</v>
+        <v>1.47</v>
       </c>
       <c r="V33" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>1.41</v>
+        <v>1.16</v>
       </c>
       <c r="X33" t="n">
-        <v>2.52</v>
+        <v>4</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.48</v>
+        <v>1.65</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="AA33" t="n">
-        <v>4.4</v>
+        <v>2.59</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.14</v>
+        <v>1.39</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.03</v>
+        <v>1.55</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.69</v>
+        <v>2.2</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
@@ -4735,10 +4735,10 @@
         </is>
       </c>
       <c r="AG33" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
@@ -4761,22 +4761,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Växjö</t>
+          <t>London City Lionesses</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>West Ham United Women</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4797,61 +4797,61 @@
         </is>
       </c>
       <c r="L34" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="M34" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="N34" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>0</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="Z34" t="n">
         <v>2.05</v>
       </c>
-      <c r="M34" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N34" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="O34" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="P34" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S34" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T34" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="V34" t="n">
-        <v>0</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="X34" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>2.11</v>
-      </c>
       <c r="AA34" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
@@ -4864,10 +4864,10 @@
         </is>
       </c>
       <c r="AG34" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AI34" t="n">
         <v>0</v>
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>London City Lionesses</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>West Ham United Women</t>
+          <t>Leicester City WFC</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4926,61 +4926,61 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.88</v>
+        <v>1.62</v>
       </c>
       <c r="M35" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="N35" t="n">
-        <v>3.55</v>
+        <v>4.8</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>5.48</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="Z35" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AE35" t="inlineStr">
         <is>
@@ -4993,10 +4993,10 @@
         </is>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AI35" t="n">
         <v>0</v>
@@ -5029,12 +5029,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Everton Women</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur Women</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5055,61 +5055,61 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>1.53</v>
+        <v>7</v>
       </c>
       <c r="P36" t="n">
-        <v>3</v>
+        <v>2.31</v>
       </c>
       <c r="Q36" t="n">
-        <v>9</v>
+        <v>1.75</v>
       </c>
       <c r="R36" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="S36" t="n">
-        <v>4.3</v>
+        <v>2.96</v>
       </c>
       <c r="T36" t="n">
-        <v>2.03</v>
+        <v>2.52</v>
       </c>
       <c r="U36" t="n">
-        <v>1.85</v>
+        <v>1.44</v>
       </c>
       <c r="V36" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W36" t="n">
-        <v>1.08</v>
+        <v>1.17</v>
       </c>
       <c r="X36" t="n">
-        <v>6</v>
+        <v>4.2</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.9</v>
+        <v>2.8</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.91</v>
+        <v>2.12</v>
       </c>
       <c r="AD36" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AE36" t="inlineStr">
         <is>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="AG36" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AH36" t="n">
-        <v>4.5</v>
+        <v>1.06</v>
       </c>
       <c r="AI36" t="n">
         <v>0</v>
@@ -5148,22 +5148,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Everton Women</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5184,61 +5184,61 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O37" t="n">
-        <v>7</v>
+        <v>2.68</v>
       </c>
       <c r="P37" t="n">
-        <v>2.31</v>
+        <v>1.99</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.75</v>
+        <v>4.76</v>
       </c>
       <c r="R37" t="n">
-        <v>1.33</v>
+        <v>1.55</v>
       </c>
       <c r="S37" t="n">
-        <v>2.96</v>
+        <v>2.33</v>
       </c>
       <c r="T37" t="n">
-        <v>2.52</v>
+        <v>3.44</v>
       </c>
       <c r="U37" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="V37" t="n">
         <v>1.04</v>
       </c>
       <c r="W37" t="n">
-        <v>1.17</v>
+        <v>1.5</v>
       </c>
       <c r="X37" t="n">
-        <v>4.2</v>
+        <v>2.52</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.67</v>
+        <v>2.3</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.1</v>
+        <v>1.55</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.8</v>
+        <v>4.1</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.4</v>
+        <v>1.14</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.12</v>
+        <v>2.03</v>
       </c>
       <c r="AD37" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AE37" t="inlineStr">
         <is>
@@ -5251,10 +5251,10 @@
         </is>
       </c>
       <c r="AG37" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AH37" t="n">
-        <v>1.06</v>
+        <v>1.66</v>
       </c>
       <c r="AI37" t="n">
         <v>0</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Leicester City WFC</t>
+          <t>Tottenham Hotspur Women</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5313,61 +5313,61 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.62</v>
+        <v>1.18</v>
       </c>
       <c r="M38" t="n">
-        <v>3.85</v>
+        <v>6.8</v>
       </c>
       <c r="N38" t="n">
-        <v>4.8</v>
+        <v>11.5</v>
       </c>
       <c r="O38" t="n">
-        <v>2.01</v>
+        <v>1.53</v>
       </c>
       <c r="P38" t="n">
-        <v>2.45</v>
+        <v>3</v>
       </c>
       <c r="Q38" t="n">
-        <v>5.48</v>
+        <v>9</v>
       </c>
       <c r="R38" t="n">
-        <v>1.31</v>
+        <v>1.18</v>
       </c>
       <c r="S38" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="T38" t="n">
-        <v>2.46</v>
+        <v>2.03</v>
       </c>
       <c r="U38" t="n">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="V38" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="W38" t="n">
-        <v>1.23</v>
+        <v>1.08</v>
       </c>
       <c r="X38" t="n">
-        <v>3.85</v>
+        <v>6</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.7</v>
+        <v>1.36</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.02</v>
+        <v>2.9</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.56</v>
+        <v>1.9</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="AE38" t="inlineStr">
         <is>
@@ -5380,10 +5380,10 @@
         </is>
       </c>
       <c r="AG38" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AH38" t="n">
-        <v>2.3</v>
+        <v>4.5</v>
       </c>
       <c r="AI38" t="n">
         <v>0</v>
@@ -5451,52 +5451,52 @@
         <v>2.55</v>
       </c>
       <c r="O39" t="n">
-        <v>3.82</v>
+        <v>3.86</v>
       </c>
       <c r="P39" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.98</v>
+        <v>2.9</v>
       </c>
       <c r="R39" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S39" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="T39" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="U39" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="V39" t="n">
         <v>1.01</v>
       </c>
       <c r="W39" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="X39" t="n">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="Y39" t="n">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AA39" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AD39" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="AE39" t="inlineStr">
         <is>
@@ -5509,10 +5509,10 @@
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>1.27</v>
+        <v>1.54</v>
       </c>
       <c r="AH39" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AI39" t="n">
         <v>0</v>
@@ -5580,19 +5580,19 @@
         <v>3.15</v>
       </c>
       <c r="O40" t="n">
-        <v>3.5</v>
+        <v>3.62</v>
       </c>
       <c r="P40" t="n">
         <v>1.91</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="R40" t="n">
         <v>1.47</v>
       </c>
       <c r="S40" t="n">
-        <v>2.43</v>
+        <v>2.6</v>
       </c>
       <c r="T40" t="n">
         <v>3.08</v>
@@ -5610,16 +5610,16 @@
         <v>2.74</v>
       </c>
       <c r="Y40" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="AA40" t="n">
-        <v>3.92</v>
+        <v>4.1</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AC40" t="n">
         <v>1.86</v>
@@ -5638,7 +5638,7 @@
         </is>
       </c>
       <c r="AG40" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AH40" t="n">
         <v>1.36</v>
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5803,12 +5803,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ceuta</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6087,13 +6087,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>3.81</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6126,10 +6126,10 @@
         <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
         <v>0</v>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Ceuta</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6216,13 +6216,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6255,10 +6255,10 @@
         <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AA45" t="n">
         <v>0</v>
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Audace Cerignola</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6474,61 +6474,61 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="M47" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="N47" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="O47" t="n">
-        <v>2.8</v>
+        <v>3.12</v>
       </c>
       <c r="P47" t="n">
         <v>1.99</v>
       </c>
       <c r="Q47" t="n">
-        <v>4.44</v>
+        <v>3.38</v>
       </c>
       <c r="R47" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="S47" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="T47" t="n">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="U47" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="V47" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W47" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="X47" t="n">
-        <v>2.74</v>
+        <v>3.5</v>
       </c>
       <c r="Y47" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AA47" t="n">
-        <v>3.82</v>
+        <v>3</v>
       </c>
       <c r="AB47" t="n">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.88</v>
+        <v>1.74</v>
       </c>
       <c r="AD47" t="n">
-        <v>1.81</v>
+        <v>1.93</v>
       </c>
       <c r="AE47" t="inlineStr">
         <is>
@@ -6541,10 +6541,10 @@
         </is>
       </c>
       <c r="AG47" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="AH47" t="n">
-        <v>1.62</v>
+        <v>1.43</v>
       </c>
       <c r="AI47" t="n">
         <v>0</v>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Cavese</t>
+          <t>NAC Breda W</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6603,13 +6603,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6642,10 +6642,10 @@
         <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
         <v>0</v>
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Heerenveen W</t>
+          <t>Cavese</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>HERA</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6732,13 +6732,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6771,10 +6771,10 @@
         <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AA49" t="n">
         <v>0</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Siracusa</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Sorrento Calcio</t>
+          <t>Excelsior Barendrecht W</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,61 +7119,61 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.88</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="U52" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V52" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W52" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="X52" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Z52" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD52" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AE52" t="inlineStr">
         <is>
@@ -7186,10 +7186,10 @@
         </is>
       </c>
       <c r="AG52" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH52" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AI52" t="n">
         <v>0</v>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7222,12 +7222,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>NAC Breda W</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7248,61 +7248,61 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>4.44</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V53" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W53" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AD53" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AE53" t="inlineStr">
         <is>
@@ -7315,10 +7315,10 @@
         </is>
       </c>
       <c r="AG53" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH53" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AI53" t="n">
         <v>0</v>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>Heerenveen W</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Excelsior Barendrecht W</t>
+          <t>HERA</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>PEC Zwolle W</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Audace Cerignola</t>
+          <t>ADO Den Haag W</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,61 +7506,61 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>2.58</v>
+        <v>0</v>
       </c>
       <c r="T55" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="U55" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V55" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W55" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="X55" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Z55" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AA55" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC55" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AD55" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AE55" t="inlineStr">
         <is>
@@ -7573,10 +7573,10 @@
         </is>
       </c>
       <c r="AG55" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH55" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AI55" t="n">
         <v>0</v>
@@ -7599,7 +7599,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>PEC Zwolle W</t>
+          <t>Siracusa</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>ADO Den Haag W</t>
+          <t>Sorrento Calcio</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,61 +7635,61 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N56" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O56" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S56" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T56" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U56" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V56" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W56" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="X56" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AC56" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD56" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE56" t="inlineStr">
         <is>
@@ -7702,10 +7702,10 @@
         </is>
       </c>
       <c r="AG56" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH56" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AI56" t="n">
         <v>0</v>
@@ -7923,10 +7923,10 @@
         <v>1.3</v>
       </c>
       <c r="V58" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="W58" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="X58" t="n">
         <v>2.85</v>
@@ -7941,7 +7941,7 @@
         <v>3.8</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AC58" t="n">
         <v>1.8</v>
@@ -7960,10 +7960,10 @@
         </is>
       </c>
       <c r="AG58" t="n">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="AH58" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AI58" t="n">
         <v>0</v>
@@ -8037,7 +8037,7 @@
         <v>2.03</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.7</v>
+        <v>3.84</v>
       </c>
       <c r="R59" t="n">
         <v>1.4</v>
@@ -8061,7 +8061,7 @@
         <v>2.97</v>
       </c>
       <c r="Y59" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="Z59" t="n">
         <v>1.68</v>
@@ -8076,7 +8076,7 @@
         <v>1.81</v>
       </c>
       <c r="AD59" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AE59" t="inlineStr">
         <is>
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -8373,7 +8373,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -8383,12 +8383,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Arenteiro</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Guadalajara</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8409,61 +8409,61 @@
         </is>
       </c>
       <c r="L62" t="n">
-        <v>3.15</v>
+        <v>2.6</v>
       </c>
       <c r="M62" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
       <c r="N62" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="O62" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="T62" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="U62" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V62" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W62" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="X62" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Y62" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z62" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA62" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AC62" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD62" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AE62" t="inlineStr">
         <is>
@@ -8476,10 +8476,10 @@
         </is>
       </c>
       <c r="AG62" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AH62" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AI62" t="n">
         <v>0</v>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8631,7 +8631,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -8641,12 +8641,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Arenteiro</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Guadalajara</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8667,61 +8667,61 @@
         </is>
       </c>
       <c r="L64" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="M64" t="n">
         <v>2.6</v>
       </c>
-      <c r="M64" t="n">
-        <v>3.1</v>
-      </c>
       <c r="N64" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="O64" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S64" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="T64" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="U64" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V64" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="W64" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X64" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Y64" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z64" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA64" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AB64" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AC64" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD64" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AE64" t="inlineStr">
         <is>
@@ -8734,10 +8734,10 @@
         </is>
       </c>
       <c r="AG64" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AH64" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AI64" t="n">
         <v>0</v>
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Real Madrid III</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Getafe II</t>
+          <t>SD Ponferradina</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9441,13 +9441,13 @@
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="M70" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N70" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O70" t="n">
         <v>0</v>
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Racing Santander II</t>
+          <t>Deportivo La Coruña II</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>Langreo</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9673,12 +9673,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>UD Mutilvera</t>
+          <t>Real Zaragoza II</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Náxara CD</t>
+          <t>CD Alfaro</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9699,13 +9699,13 @@
         </is>
       </c>
       <c r="L72" t="n">
-        <v>2.36</v>
+        <v>1.78</v>
       </c>
       <c r="M72" t="n">
-        <v>3.1</v>
+        <v>3.31</v>
       </c>
       <c r="N72" t="n">
-        <v>2.99</v>
+        <v>4.39</v>
       </c>
       <c r="O72" t="n">
         <v>0</v>
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>CD Ebro</t>
+          <t>UD Mutilvera</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Real Unión</t>
+          <t>Náxara CD</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9828,13 +9828,13 @@
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="M73" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N73" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="O73" t="n">
         <v>0</v>
@@ -9921,7 +9921,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -9931,12 +9931,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Utebo</t>
+          <t>Real Madrid III</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>SD Logroñés</t>
+          <t>Getafe II</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -9957,13 +9957,13 @@
         </is>
       </c>
       <c r="L74" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="M74" t="n">
-        <v>3.12</v>
+        <v>0</v>
       </c>
       <c r="N74" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O74" t="n">
         <v>0</v>
@@ -10060,12 +10060,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Club Marino de Luanco</t>
+          <t>CD Numancia</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Gimnástica Segoviana CF</t>
+          <t>Sámano</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10086,13 +10086,13 @@
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="M75" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N75" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="O75" t="n">
         <v>0</v>
@@ -10125,10 +10125,10 @@
         <v>0</v>
       </c>
       <c r="Y75" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z75" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA75" t="n">
         <v>0</v>
@@ -10179,7 +10179,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Real Ávila</t>
+          <t>CD Ebro</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Real Oviedo II</t>
+          <t>Real Unión</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10215,13 +10215,13 @@
         </is>
       </c>
       <c r="L76" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="N76" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O76" t="n">
         <v>0</v>
@@ -10254,10 +10254,10 @@
         <v>0</v>
       </c>
       <c r="Y76" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z76" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AA76" t="n">
         <v>0</v>
@@ -10308,7 +10308,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña II</t>
+          <t>Barakaldo CF</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Langreo</t>
+          <t>Athletic Club II</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10344,13 +10344,13 @@
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="M77" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N77" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -10566,7 +10566,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -10576,12 +10576,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Unionistas de Salamanca CF</t>
+          <t>Salamanca CF UDS</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mérida AD</t>
+          <t>Sarriana</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10602,13 +10602,13 @@
         </is>
       </c>
       <c r="L79" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="N79" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="O79" t="n">
         <v>0</v>
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Yeclano Deportivo</t>
+          <t>Gernika Club</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Puente Genil</t>
+          <t>SD Amorebieta</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10731,13 +10731,13 @@
         </is>
       </c>
       <c r="L80" t="n">
-        <v>1.91</v>
+        <v>2.62</v>
       </c>
       <c r="M80" t="n">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="N80" t="n">
-        <v>3.9</v>
+        <v>2.75</v>
       </c>
       <c r="O80" t="n">
         <v>0</v>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Águilas FC</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Antoniano</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10860,61 +10860,61 @@
         </is>
       </c>
       <c r="L81" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N81" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="O81" t="n">
-        <v>4.67</v>
+        <v>0</v>
       </c>
       <c r="P81" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="S81" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="T81" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="U81" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="V81" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="W81" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="X81" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="Y81" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z81" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA81" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="AB81" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AC81" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD81" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AE81" t="inlineStr">
         <is>
@@ -10927,10 +10927,10 @@
         </is>
       </c>
       <c r="AG81" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH81" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AI81" t="n">
         <v>0</v>
@@ -10953,7 +10953,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -10963,12 +10963,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>CD Numancia</t>
+          <t>Utebo</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Sámano</t>
+          <t>SD Logroñés</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -10989,13 +10989,13 @@
         </is>
       </c>
       <c r="L82" t="n">
-        <v>1.35</v>
+        <v>2.57</v>
       </c>
       <c r="M82" t="n">
-        <v>4.6</v>
+        <v>3.12</v>
       </c>
       <c r="N82" t="n">
-        <v>7.8</v>
+        <v>2.65</v>
       </c>
       <c r="O82" t="n">
         <v>0</v>
@@ -11028,10 +11028,10 @@
         <v>0</v>
       </c>
       <c r="Y82" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z82" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA82" t="n">
         <v>0</v>
@@ -11082,7 +11082,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>UD Barbastro</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Torrent</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11118,22 +11118,22 @@
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O83" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q83" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="R83" t="n">
         <v>0</v>
@@ -11142,37 +11142,37 @@
         <v>0</v>
       </c>
       <c r="T83" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U83" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V83" t="n">
         <v>0</v>
       </c>
       <c r="W83" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X83" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="Y83" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Z83" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AA83" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB83" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC83" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD83" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE83" t="inlineStr">
         <is>
@@ -11185,10 +11185,10 @@
         </is>
       </c>
       <c r="AG83" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH83" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AI83" t="n">
         <v>0</v>
@@ -11211,7 +11211,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -11221,12 +11221,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Águilas FC</t>
+          <t>Club Marino de Luanco</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Antoniano</t>
+          <t>Gimnástica Segoviana CF</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11340,7 +11340,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -11350,12 +11350,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Real Zaragoza II</t>
+          <t>Celta de Vigo II</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>CD Alfaro</t>
+          <t>Ourense CF</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11376,13 +11376,13 @@
         </is>
       </c>
       <c r="L85" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="M85" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="N85" t="n">
-        <v>4.39</v>
+        <v>0</v>
       </c>
       <c r="O85" t="n">
         <v>0</v>
@@ -11469,22 +11469,22 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Barcelona II</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Reddis</t>
+          <t>Huachipato</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11505,13 +11505,13 @@
         </is>
       </c>
       <c r="L86" t="n">
-        <v>1.57</v>
+        <v>2.15</v>
       </c>
       <c r="M86" t="n">
-        <v>3.67</v>
+        <v>3.5</v>
       </c>
       <c r="N86" t="n">
-        <v>5</v>
+        <v>3.1</v>
       </c>
       <c r="O86" t="n">
         <v>0</v>
@@ -11544,10 +11544,10 @@
         <v>0</v>
       </c>
       <c r="Y86" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z86" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA86" t="n">
         <v>0</v>
@@ -11727,7 +11727,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>Real Ávila</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>SD Ponferradina</t>
+          <t>Real Oviedo II</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11763,13 +11763,13 @@
         </is>
       </c>
       <c r="L88" t="n">
-        <v>2.97</v>
+        <v>2.4</v>
       </c>
       <c r="M88" t="n">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="N88" t="n">
-        <v>2.2</v>
+        <v>2.65</v>
       </c>
       <c r="O88" t="n">
         <v>0</v>
@@ -11802,10 +11802,10 @@
         <v>0</v>
       </c>
       <c r="Y88" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z88" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AA88" t="n">
         <v>0</v>
@@ -11856,7 +11856,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -11866,12 +11866,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Barakaldo CF</t>
+          <t>UD Barbastro</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Athletic Club II</t>
+          <t>Torrent</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11892,13 +11892,13 @@
         </is>
       </c>
       <c r="L89" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="M89" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N89" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
         <v>0</v>
@@ -11985,7 +11985,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 1</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Celta de Vigo II</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ourense CF</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12021,61 +12021,61 @@
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="M90" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N90" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="O90" t="n">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="Q90" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="R90" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S90" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T90" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="U90" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="V90" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="W90" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="X90" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="Y90" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z90" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA90" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AB90" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AC90" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AD90" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AE90" t="inlineStr">
         <is>
@@ -12088,10 +12088,10 @@
         </is>
       </c>
       <c r="AG90" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH90" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AI90" t="n">
         <v>0</v>
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Spain Primera Division RFEF Group 1</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Unionistas de Salamanca CF</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Mérida AD</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12150,22 +12150,22 @@
         </is>
       </c>
       <c r="L91" t="n">
-        <v>1.59</v>
+        <v>2.14</v>
       </c>
       <c r="M91" t="n">
-        <v>3.8</v>
+        <v>3.05</v>
       </c>
       <c r="N91" t="n">
-        <v>4.9</v>
+        <v>2.65</v>
       </c>
       <c r="O91" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="P91" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="R91" t="n">
         <v>0</v>
@@ -12174,37 +12174,37 @@
         <v>0</v>
       </c>
       <c r="T91" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="U91" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="V91" t="n">
         <v>0</v>
       </c>
       <c r="W91" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="X91" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Y91" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="Z91" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AA91" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AB91" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC91" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD91" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AE91" t="inlineStr">
         <is>
@@ -12217,10 +12217,10 @@
         </is>
       </c>
       <c r="AG91" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH91" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AI91" t="n">
         <v>0</v>
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Salamanca CF UDS</t>
+          <t>Racing Santander II</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Sarriana</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Gernika Club</t>
+          <t>Yeclano Deportivo</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>SD Amorebieta</t>
+          <t>Puente Genil</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12408,13 +12408,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>2.62</v>
+        <v>1.91</v>
       </c>
       <c r="M93" t="n">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="N93" t="n">
-        <v>2.75</v>
+        <v>3.9</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12501,22 +12501,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Barcelona II</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Huachipato</t>
+          <t>Reddis</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12537,13 +12537,13 @@
         </is>
       </c>
       <c r="L94" t="n">
-        <v>2.15</v>
+        <v>1.57</v>
       </c>
       <c r="M94" t="n">
-        <v>3.5</v>
+        <v>3.67</v>
       </c>
       <c r="N94" t="n">
-        <v>3.1</v>
+        <v>5</v>
       </c>
       <c r="O94" t="n">
         <v>0</v>
@@ -12576,10 +12576,10 @@
         <v>0</v>
       </c>
       <c r="Y94" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Z94" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AA94" t="n">
         <v>0</v>
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Sestao River Club</t>
+          <t>Benevento</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>CD Tudelano</t>
+          <t>Team Altamura</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12666,61 +12666,61 @@
         </is>
       </c>
       <c r="L95" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="M95" t="n">
-        <v>3.3</v>
+        <v>3.85</v>
       </c>
       <c r="N95" t="n">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
       <c r="O95" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Q95" t="n">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="R95" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S95" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="T95" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="U95" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="V95" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W95" t="n">
-        <v>1.52</v>
+        <v>1.25</v>
       </c>
       <c r="X95" t="n">
-        <v>2.35</v>
+        <v>3.58</v>
       </c>
       <c r="Y95" t="n">
-        <v>2.35</v>
+        <v>1.85</v>
       </c>
       <c r="Z95" t="n">
-        <v>1.57</v>
+        <v>1.85</v>
       </c>
       <c r="AA95" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AB95" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC95" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD95" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AE95" t="inlineStr">
         <is>
@@ -12733,10 +12733,10 @@
         </is>
       </c>
       <c r="AG95" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AH95" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="AI95" t="n">
         <v>0</v>
@@ -12759,22 +12759,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Inter II</t>
+          <t>Unión San Felipe</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Deportes Santa Cruz</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12795,61 +12795,61 @@
         </is>
       </c>
       <c r="L96" t="n">
-        <v>1.92</v>
+        <v>2.05</v>
       </c>
       <c r="M96" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="N96" t="n">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="O96" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="P96" t="n">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="Q96" t="n">
-        <v>5.17</v>
+        <v>4.75</v>
       </c>
       <c r="R96" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="S96" t="n">
-        <v>2.55</v>
+        <v>2.66</v>
       </c>
       <c r="T96" t="n">
-        <v>3.03</v>
+        <v>2.94</v>
       </c>
       <c r="U96" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="V96" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="W96" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="X96" t="n">
-        <v>2.88</v>
+        <v>3.08</v>
       </c>
       <c r="Y96" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="Z96" t="n">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="AA96" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="AB96" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AC96" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="AD96" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="AE96" t="inlineStr">
         <is>
@@ -12862,10 +12862,10 @@
         </is>
       </c>
       <c r="AG96" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AH96" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="AI96" t="n">
         <v>0</v>
@@ -12888,22 +12888,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Unión San Felipe</t>
+          <t>Sestao River Club</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Deportes Santa Cruz</t>
+          <t>CD Tudelano</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,61 +12924,61 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="M97" t="n">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="N97" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="O97" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="P97" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="Q97" t="n">
-        <v>4.58</v>
+        <v>0</v>
       </c>
       <c r="R97" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S97" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T97" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="U97" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V97" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W97" t="n">
-        <v>1.3</v>
+        <v>1.52</v>
       </c>
       <c r="X97" t="n">
-        <v>2.97</v>
+        <v>2.35</v>
       </c>
       <c r="Y97" t="n">
-        <v>2.04</v>
+        <v>2.35</v>
       </c>
       <c r="Z97" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="AA97" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AB97" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AC97" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AD97" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AE97" t="inlineStr">
         <is>
@@ -12991,10 +12991,10 @@
         </is>
       </c>
       <c r="AG97" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AH97" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AI97" t="n">
         <v>0</v>
@@ -13017,7 +13017,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Ascoli</t>
+          <t>Inter II</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13053,61 +13053,61 @@
         </is>
       </c>
       <c r="L98" t="n">
-        <v>1.5</v>
+        <v>1.92</v>
       </c>
       <c r="M98" t="n">
-        <v>4.05</v>
+        <v>3.4</v>
       </c>
       <c r="N98" t="n">
-        <v>6.1</v>
+        <v>3.75</v>
       </c>
       <c r="O98" t="n">
-        <v>1.86</v>
+        <v>2.35</v>
       </c>
       <c r="P98" t="n">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="Q98" t="n">
-        <v>10.7</v>
+        <v>5.17</v>
       </c>
       <c r="R98" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="S98" t="n">
-        <v>2.46</v>
+        <v>2.55</v>
       </c>
       <c r="T98" t="n">
-        <v>3.05</v>
+        <v>3.03</v>
       </c>
       <c r="U98" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="V98" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W98" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="X98" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
       <c r="Y98" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="Z98" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AA98" t="n">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="AB98" t="n">
         <v>1.22</v>
       </c>
       <c r="AC98" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="AD98" t="n">
-        <v>1.43</v>
+        <v>1.79</v>
       </c>
       <c r="AE98" t="inlineStr">
         <is>
@@ -13120,10 +13120,10 @@
         </is>
       </c>
       <c r="AG98" t="n">
-        <v>1.15</v>
+        <v>1.25</v>
       </c>
       <c r="AH98" t="n">
-        <v>3.02</v>
+        <v>1.86</v>
       </c>
       <c r="AI98" t="n">
         <v>0</v>
@@ -13275,7 +13275,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Benevento</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Team Altamura</t>
+          <t>Lecco</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13311,77 +13311,77 @@
         </is>
       </c>
       <c r="L100" t="n">
-        <v>1.53</v>
+        <v>2.03</v>
       </c>
       <c r="M100" t="n">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="N100" t="n">
-        <v>5.9</v>
+        <v>3.4</v>
       </c>
       <c r="O100" t="n">
-        <v>1.86</v>
+        <v>3.56</v>
       </c>
       <c r="P100" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="R100" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S100" t="n">
         <v>2.57</v>
       </c>
-      <c r="Q100" t="n">
-        <v>8.25</v>
-      </c>
-      <c r="R100" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S100" t="n">
-        <v>2.99</v>
-      </c>
       <c r="T100" t="n">
-        <v>2.54</v>
+        <v>3.05</v>
       </c>
       <c r="U100" t="n">
-        <v>1.47</v>
+        <v>1.31</v>
       </c>
       <c r="V100" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="W100" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="X100" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="Y100" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z100" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA100" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB100" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC100" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD100" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AE100" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF100" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG100" t="n">
         <v>1.25</v>
       </c>
-      <c r="X100" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="Y100" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z100" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA100" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AB100" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC100" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AD100" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AE100" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF100" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG100" t="n">
-        <v>1.11</v>
-      </c>
       <c r="AH100" t="n">
-        <v>3.12</v>
+        <v>1.42</v>
       </c>
       <c r="AI100" t="n">
         <v>0</v>
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Ascoli</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Lecco</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13440,28 +13440,28 @@
         </is>
       </c>
       <c r="L101" t="n">
-        <v>2.03</v>
+        <v>1.5</v>
       </c>
       <c r="M101" t="n">
-        <v>3.4</v>
+        <v>4.05</v>
       </c>
       <c r="N101" t="n">
-        <v>3.4</v>
+        <v>6.1</v>
       </c>
       <c r="O101" t="n">
-        <v>3.56</v>
+        <v>1.86</v>
       </c>
       <c r="P101" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="Q101" t="n">
-        <v>3.16</v>
+        <v>10.7</v>
       </c>
       <c r="R101" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="S101" t="n">
-        <v>2.57</v>
+        <v>2.46</v>
       </c>
       <c r="T101" t="n">
         <v>3.05</v>
@@ -13470,31 +13470,31 @@
         <v>1.31</v>
       </c>
       <c r="V101" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W101" t="n">
-        <v>1.39</v>
+        <v>1.31</v>
       </c>
       <c r="X101" t="n">
-        <v>2.78</v>
+        <v>2.92</v>
       </c>
       <c r="Y101" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="Z101" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AA101" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AB101" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AC101" t="n">
-        <v>1.83</v>
+        <v>2.6</v>
       </c>
       <c r="AD101" t="n">
-        <v>1.83</v>
+        <v>1.43</v>
       </c>
       <c r="AE101" t="inlineStr">
         <is>
@@ -13507,10 +13507,10 @@
         </is>
       </c>
       <c r="AG101" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AH101" t="n">
-        <v>1.42</v>
+        <v>3.02</v>
       </c>
       <c r="AI101" t="n">
         <v>0</v>
@@ -13662,7 +13662,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 2</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>UD Logroñés</t>
+          <t>Xerez CD</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Beasain</t>
+          <t>Almería II</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13698,13 +13698,13 @@
         </is>
       </c>
       <c r="L103" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="M103" t="n">
-        <v>3.85</v>
+        <v>3.2</v>
       </c>
       <c r="N103" t="n">
-        <v>5.9</v>
+        <v>4.6</v>
       </c>
       <c r="O103" t="n">
         <v>0</v>
@@ -13737,10 +13737,10 @@
         <v>0</v>
       </c>
       <c r="Y103" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Z103" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="AA103" t="n">
         <v>0</v>
@@ -13791,7 +13791,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 2</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Espanyol II</t>
+          <t>UD Logroñés</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Atlètic Lleida</t>
+          <t>Beasain</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13827,13 +13827,13 @@
         </is>
       </c>
       <c r="L104" t="n">
-        <v>2.08</v>
+        <v>1.53</v>
       </c>
       <c r="M104" t="n">
-        <v>3.15</v>
+        <v>3.85</v>
       </c>
       <c r="N104" t="n">
-        <v>3.55</v>
+        <v>5.9</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -13866,10 +13866,10 @@
         <v>0</v>
       </c>
       <c r="Y104" t="n">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="Z104" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AA104" t="n">
         <v>0</v>
@@ -13920,7 +13920,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 3</t>
+          <t>Spain Segunda División RFEF Group 4</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>UE Olot</t>
+          <t>CF Lorca Deportiva</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Terrassa FC</t>
+          <t>Extremadura 1924</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -13956,13 +13956,13 @@
         </is>
       </c>
       <c r="L105" t="n">
-        <v>2.45</v>
+        <v>4.2</v>
       </c>
       <c r="M105" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="N105" t="n">
-        <v>2.95</v>
+        <v>1.8</v>
       </c>
       <c r="O105" t="n">
         <v>0</v>
@@ -13995,10 +13995,10 @@
         <v>0</v>
       </c>
       <c r="Y105" t="n">
-        <v>2.4</v>
+        <v>2.02</v>
       </c>
       <c r="Z105" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AA105" t="n">
         <v>0</v>
@@ -14178,7 +14178,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -14188,12 +14188,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>CF Lorca Deportiva</t>
+          <t>UE Olot</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Extremadura 1924</t>
+          <t>Terrassa FC</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -14214,13 +14214,13 @@
         </is>
       </c>
       <c r="L107" t="n">
-        <v>4.2</v>
+        <v>2.45</v>
       </c>
       <c r="M107" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="N107" t="n">
-        <v>1.8</v>
+        <v>2.95</v>
       </c>
       <c r="O107" t="n">
         <v>0</v>
@@ -14253,10 +14253,10 @@
         <v>0</v>
       </c>
       <c r="Y107" t="n">
-        <v>2.02</v>
+        <v>2.4</v>
       </c>
       <c r="Z107" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AA107" t="n">
         <v>0</v>
@@ -14307,7 +14307,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 4</t>
+          <t>Spain Segunda División RFEF Group 3</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Xerez CD</t>
+          <t>Espanyol II</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Almería II</t>
+          <t>Atlètic Lleida</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14343,13 +14343,13 @@
         </is>
       </c>
       <c r="L108" t="n">
-        <v>1.8</v>
+        <v>2.08</v>
       </c>
       <c r="M108" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="N108" t="n">
-        <v>4.6</v>
+        <v>3.55</v>
       </c>
       <c r="O108" t="n">
         <v>0</v>
@@ -14382,10 +14382,10 @@
         <v>0</v>
       </c>
       <c r="Y108" t="n">
-        <v>2.12</v>
+        <v>2.35</v>
       </c>
       <c r="Z108" t="n">
-        <v>1.64</v>
+        <v>1.53</v>
       </c>
       <c r="AA108" t="n">
         <v>0</v>
@@ -14575,12 +14575,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Real Valladolid</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14601,22 +14601,22 @@
         </is>
       </c>
       <c r="L110" t="n">
-        <v>2.6</v>
+        <v>1.87</v>
       </c>
       <c r="M110" t="n">
-        <v>2.89</v>
+        <v>3.1</v>
       </c>
       <c r="N110" t="n">
-        <v>2.95</v>
+        <v>4.7</v>
       </c>
       <c r="O110" t="n">
-        <v>3.45</v>
+        <v>2.85</v>
       </c>
       <c r="P110" t="n">
-        <v>1.95</v>
+        <v>1.88</v>
       </c>
       <c r="Q110" t="n">
-        <v>3.65</v>
+        <v>4.3</v>
       </c>
       <c r="R110" t="n">
         <v>1.53</v>
@@ -14625,37 +14625,37 @@
         <v>2.38</v>
       </c>
       <c r="T110" t="n">
-        <v>3.66</v>
+        <v>3.7</v>
       </c>
       <c r="U110" t="n">
         <v>1.25</v>
       </c>
       <c r="V110" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="W110" t="n">
-        <v>1.48</v>
+        <v>1.58</v>
       </c>
       <c r="X110" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="Y110" t="n">
-        <v>2.55</v>
+        <v>2.65</v>
       </c>
       <c r="Z110" t="n">
-        <v>1.52</v>
+        <v>1.41</v>
       </c>
       <c r="AA110" t="n">
-        <v>4.95</v>
+        <v>5.32</v>
       </c>
       <c r="AB110" t="n">
         <v>1.14</v>
       </c>
       <c r="AC110" t="n">
-        <v>2.05</v>
+        <v>2.22</v>
       </c>
       <c r="AD110" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AE110" t="inlineStr">
         <is>
@@ -14671,7 +14671,7 @@
         <v>1.4</v>
       </c>
       <c r="AH110" t="n">
-        <v>1.44</v>
+        <v>1.82</v>
       </c>
       <c r="AI110" t="n">
         <v>0</v>
@@ -14704,12 +14704,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Cádiz</t>
+          <t>Burgos CF</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Real Valladolid</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14730,22 +14730,22 @@
         </is>
       </c>
       <c r="L111" t="n">
-        <v>1.87</v>
+        <v>2.6</v>
       </c>
       <c r="M111" t="n">
-        <v>3.1</v>
+        <v>2.89</v>
       </c>
       <c r="N111" t="n">
-        <v>4.7</v>
+        <v>2.95</v>
       </c>
       <c r="O111" t="n">
-        <v>2.85</v>
+        <v>3.45</v>
       </c>
       <c r="P111" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="Q111" t="n">
-        <v>4.3</v>
+        <v>3.65</v>
       </c>
       <c r="R111" t="n">
         <v>1.53</v>
@@ -14754,37 +14754,37 @@
         <v>2.38</v>
       </c>
       <c r="T111" t="n">
-        <v>3.7</v>
+        <v>3.66</v>
       </c>
       <c r="U111" t="n">
         <v>1.25</v>
       </c>
       <c r="V111" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="W111" t="n">
-        <v>1.58</v>
+        <v>1.48</v>
       </c>
       <c r="X111" t="n">
-        <v>2.35</v>
+        <v>2.4</v>
       </c>
       <c r="Y111" t="n">
-        <v>2.65</v>
+        <v>2.55</v>
       </c>
       <c r="Z111" t="n">
-        <v>1.41</v>
+        <v>1.52</v>
       </c>
       <c r="AA111" t="n">
-        <v>5.32</v>
+        <v>4.95</v>
       </c>
       <c r="AB111" t="n">
         <v>1.14</v>
       </c>
       <c r="AC111" t="n">
-        <v>2.22</v>
+        <v>2.05</v>
       </c>
       <c r="AD111" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AE111" t="inlineStr">
         <is>
@@ -14800,7 +14800,7 @@
         <v>1.4</v>
       </c>
       <c r="AH111" t="n">
-        <v>1.82</v>
+        <v>1.44</v>
       </c>
       <c r="AI111" t="n">
         <v>0</v>
@@ -14952,22 +14952,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Rayo Majadahonda</t>
+          <t>Cobreloa</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>CD Coria</t>
+          <t>Deportes Temuco</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -14988,61 +14988,61 @@
         </is>
       </c>
       <c r="L113" t="n">
-        <v>2.03</v>
+        <v>1.6</v>
       </c>
       <c r="M113" t="n">
-        <v>3.1</v>
+        <v>3.95</v>
       </c>
       <c r="N113" t="n">
-        <v>3.75</v>
+        <v>4.9</v>
       </c>
       <c r="O113" t="n">
-        <v>3.28</v>
+        <v>2.18</v>
       </c>
       <c r="P113" t="n">
-        <v>1.84</v>
+        <v>2.2</v>
       </c>
       <c r="Q113" t="n">
-        <v>3.87</v>
+        <v>5.21</v>
       </c>
       <c r="R113" t="n">
-        <v>1.54</v>
+        <v>1.33</v>
       </c>
       <c r="S113" t="n">
-        <v>2.39</v>
+        <v>2.96</v>
       </c>
       <c r="T113" t="n">
-        <v>3.32</v>
+        <v>2.62</v>
       </c>
       <c r="U113" t="n">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="V113" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="W113" t="n">
-        <v>1.42</v>
+        <v>1.22</v>
       </c>
       <c r="X113" t="n">
-        <v>2.49</v>
+        <v>3.5</v>
       </c>
       <c r="Y113" t="n">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="Z113" t="n">
-        <v>1.55</v>
+        <v>1.95</v>
       </c>
       <c r="AA113" t="n">
-        <v>4.3</v>
+        <v>2.92</v>
       </c>
       <c r="AB113" t="n">
-        <v>1.15</v>
+        <v>1.31</v>
       </c>
       <c r="AC113" t="n">
-        <v>1.97</v>
+        <v>1.78</v>
       </c>
       <c r="AD113" t="n">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="AE113" t="inlineStr">
         <is>
@@ -15055,10 +15055,10 @@
         </is>
       </c>
       <c r="AG113" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AH113" t="n">
-        <v>1.44</v>
+        <v>2.15</v>
       </c>
       <c r="AI113" t="n">
         <v>0</v>
@@ -15081,22 +15081,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Cobreloa</t>
+          <t>Rayo Majadahonda</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Deportes Temuco</t>
+          <t>CD Coria</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15117,61 +15117,61 @@
         </is>
       </c>
       <c r="L114" t="n">
-        <v>1.61</v>
+        <v>2.03</v>
       </c>
       <c r="M114" t="n">
-        <v>3.6</v>
+        <v>3.1</v>
       </c>
       <c r="N114" t="n">
-        <v>5</v>
+        <v>3.75</v>
       </c>
       <c r="O114" t="n">
-        <v>2.18</v>
+        <v>3.28</v>
       </c>
       <c r="P114" t="n">
-        <v>2.2</v>
+        <v>1.84</v>
       </c>
       <c r="Q114" t="n">
-        <v>5.21</v>
+        <v>3.87</v>
       </c>
       <c r="R114" t="n">
-        <v>1.33</v>
+        <v>1.54</v>
       </c>
       <c r="S114" t="n">
-        <v>2.94</v>
+        <v>2.39</v>
       </c>
       <c r="T114" t="n">
-        <v>2.66</v>
+        <v>3.32</v>
       </c>
       <c r="U114" t="n">
-        <v>1.4</v>
+        <v>1.25</v>
       </c>
       <c r="V114" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="W114" t="n">
-        <v>1.22</v>
+        <v>1.42</v>
       </c>
       <c r="X114" t="n">
-        <v>3.5</v>
+        <v>2.49</v>
       </c>
       <c r="Y114" t="n">
-        <v>1.81</v>
+        <v>2.25</v>
       </c>
       <c r="Z114" t="n">
-        <v>1.91</v>
+        <v>1.55</v>
       </c>
       <c r="AA114" t="n">
-        <v>2.92</v>
+        <v>4.3</v>
       </c>
       <c r="AB114" t="n">
-        <v>1.31</v>
+        <v>1.15</v>
       </c>
       <c r="AC114" t="n">
-        <v>1.79</v>
+        <v>1.97</v>
       </c>
       <c r="AD114" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AE114" t="inlineStr">
         <is>
@@ -15184,10 +15184,10 @@
         </is>
       </c>
       <c r="AG114" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AH114" t="n">
-        <v>2.15</v>
+        <v>1.44</v>
       </c>
       <c r="AI114" t="n">
         <v>0</v>
@@ -15210,7 +15210,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -15220,12 +15220,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Union Brescia</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15246,61 +15246,61 @@
         </is>
       </c>
       <c r="L115" t="n">
-        <v>3.95</v>
+        <v>2.4</v>
       </c>
       <c r="M115" t="n">
-        <v>3.55</v>
+        <v>3.3</v>
       </c>
       <c r="N115" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O115" t="n">
+        <v>3</v>
+      </c>
+      <c r="P115" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="R115" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S115" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T115" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="U115" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V115" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W115" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="X115" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="Y115" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Z115" t="n">
         <v>1.83</v>
       </c>
-      <c r="O115" t="n">
-        <v>0</v>
-      </c>
-      <c r="P115" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
-      <c r="R115" t="n">
-        <v>0</v>
-      </c>
-      <c r="S115" t="n">
-        <v>0</v>
-      </c>
-      <c r="T115" t="n">
-        <v>0</v>
-      </c>
-      <c r="U115" t="n">
-        <v>0</v>
-      </c>
-      <c r="V115" t="n">
-        <v>0</v>
-      </c>
-      <c r="W115" t="n">
-        <v>0</v>
-      </c>
-      <c r="X115" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y115" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="Z115" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AA115" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AB115" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC115" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AD115" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AE115" t="inlineStr">
         <is>
@@ -15313,10 +15313,10 @@
         </is>
       </c>
       <c r="AG115" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH115" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AI115" t="n">
         <v>0</v>
@@ -15339,7 +15339,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -15349,12 +15349,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Union Brescia</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15375,61 +15375,61 @@
         </is>
       </c>
       <c r="L116" t="n">
-        <v>2.4</v>
+        <v>3.95</v>
       </c>
       <c r="M116" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="N116" t="n">
-        <v>2.75</v>
+        <v>1.83</v>
       </c>
       <c r="O116" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P116" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="Q116" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="R116" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S116" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T116" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="U116" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V116" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="W116" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="X116" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="Y116" t="n">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="Z116" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AA116" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AB116" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC116" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AD116" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AE116" t="inlineStr">
         <is>
@@ -15442,10 +15442,10 @@
         </is>
       </c>
       <c r="AG116" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AH116" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AI116" t="n">
         <v>0</v>
@@ -15666,16 +15666,16 @@
         <v>1.06</v>
       </c>
       <c r="W118" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="X118" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="Y118" t="n">
-        <v>2.63</v>
+        <v>2.55</v>
       </c>
       <c r="Z118" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AA118" t="n">
         <v>5.25</v>
@@ -15994,12 +15994,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Tivoli Gardens</t>
+          <t>Treasure Beach</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Harbour View</t>
+          <t>Waterhouse</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16020,13 +16020,13 @@
         </is>
       </c>
       <c r="L121" t="n">
-        <v>2.16</v>
+        <v>3.45</v>
       </c>
       <c r="M121" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N121" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="O121" t="n">
         <v>0</v>
@@ -16059,10 +16059,10 @@
         <v>0</v>
       </c>
       <c r="Y121" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="Z121" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="AA121" t="n">
         <v>0</v>
@@ -16381,12 +16381,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Treasure Beach</t>
+          <t>Tivoli Gardens</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Waterhouse</t>
+          <t>Harbour View</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16407,13 +16407,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>3.45</v>
+        <v>2.16</v>
       </c>
       <c r="M124" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N124" t="n">
-        <v>1.9</v>
+        <v>2.9</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -16446,10 +16446,10 @@
         <v>0</v>
       </c>
       <c r="Y124" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="Z124" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AA124" t="n">
         <v>0</v>
@@ -16510,12 +16510,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Dunbeholden</t>
+          <t>Molynes United</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Arnett Gardens</t>
+          <t>Montego Bay United</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16639,12 +16639,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Molynes United</t>
+          <t>Dunbeholden</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Montego Bay United</t>
+          <t>Arnett Gardens</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -16794,61 +16794,61 @@
         </is>
       </c>
       <c r="L127" t="n">
-        <v>1.75</v>
+        <v>1.58</v>
       </c>
       <c r="M127" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="N127" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
       <c r="O127" t="n">
-        <v>2.28</v>
+        <v>2.31</v>
       </c>
       <c r="P127" t="n">
-        <v>2.13</v>
+        <v>2.1</v>
       </c>
       <c r="Q127" t="n">
-        <v>5.1</v>
+        <v>5.11</v>
       </c>
       <c r="R127" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="S127" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="T127" t="n">
-        <v>2.78</v>
+        <v>2.94</v>
       </c>
       <c r="U127" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="V127" t="n">
         <v>1.01</v>
       </c>
       <c r="W127" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="X127" t="n">
-        <v>3.14</v>
+        <v>3.08</v>
       </c>
       <c r="Y127" t="n">
-        <v>1.92</v>
+        <v>1.75</v>
       </c>
       <c r="Z127" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AA127" t="n">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="AB127" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AC127" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AD127" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="AE127" t="inlineStr">
         <is>
@@ -16864,7 +16864,7 @@
         <v>1.24</v>
       </c>
       <c r="AH127" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="AI127" t="n">
         <v>0</v>
@@ -16932,34 +16932,34 @@
         <v>3.9</v>
       </c>
       <c r="O128" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="P128" t="n">
-        <v>2.23</v>
+        <v>2.09</v>
       </c>
       <c r="Q128" t="n">
-        <v>4.25</v>
+        <v>4.79</v>
       </c>
       <c r="R128" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S128" t="n">
-        <v>2.81</v>
+        <v>2.73</v>
       </c>
       <c r="T128" t="n">
-        <v>2.69</v>
+        <v>2.76</v>
       </c>
       <c r="U128" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="V128" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W128" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="X128" t="n">
-        <v>3.28</v>
+        <v>3.14</v>
       </c>
       <c r="Y128" t="n">
         <v>1.85</v>
@@ -16968,10 +16968,10 @@
         <v>1.85</v>
       </c>
       <c r="AA128" t="n">
-        <v>3.05</v>
+        <v>3.14</v>
       </c>
       <c r="AB128" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="AC128" t="n">
         <v>1.79</v>
@@ -16990,10 +16990,10 @@
         </is>
       </c>
       <c r="AG128" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="AH128" t="n">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="AI128" t="n">
         <v>0</v>
@@ -17052,13 +17052,13 @@
         </is>
       </c>
       <c r="L129" t="n">
-        <v>1.91</v>
+        <v>1.66</v>
       </c>
       <c r="M129" t="n">
-        <v>3</v>
+        <v>3.29</v>
       </c>
       <c r="N129" t="n">
-        <v>4.25</v>
+        <v>4.7</v>
       </c>
       <c r="O129" t="n">
         <v>2.4</v>
@@ -17091,10 +17091,10 @@
         <v>2.7</v>
       </c>
       <c r="Y129" t="n">
-        <v>2.16</v>
+        <v>2.13</v>
       </c>
       <c r="Z129" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="AA129" t="n">
         <v>4.4</v>
@@ -17181,13 +17181,13 @@
         </is>
       </c>
       <c r="L130" t="n">
-        <v>1.84</v>
+        <v>1.76</v>
       </c>
       <c r="M130" t="n">
-        <v>3.15</v>
+        <v>3.06</v>
       </c>
       <c r="N130" t="n">
-        <v>3.85</v>
+        <v>4.4</v>
       </c>
       <c r="O130" t="n">
         <v>2.57</v>
@@ -17214,16 +17214,16 @@
         <v>1.1</v>
       </c>
       <c r="W130" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="X130" t="n">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="Y130" t="n">
-        <v>2.65</v>
+        <v>2.3</v>
       </c>
       <c r="Z130" t="n">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="AA130" t="n">
         <v>5.3</v>
@@ -17568,13 +17568,13 @@
         </is>
       </c>
       <c r="L133" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="M133" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="N133" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="O133" t="n">
         <v>3.1</v>
@@ -17601,16 +17601,16 @@
         <v>1.1</v>
       </c>
       <c r="W133" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="X133" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="Y133" t="n">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="Z133" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AA133" t="n">
         <v>4.75</v>
